--- a/CodeSystem-ACCESSEventTypeCS.xlsx
+++ b/CodeSystem-ACCESSEventTypeCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T23:16:42-05:00</t>
+    <t>2026-03-06T16:03:26-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -159,7 +159,7 @@
     <t>Control Group Period Ending</t>
   </si>
   <si>
-    <t>The 12-month control group assignment period is ending soon, allowing the patient to be aligned to a participant.</t>
+    <t>The 12-month control group assignment period is ending soon, allowing the patient to be reconsidered for alignment in the ACCESS Model.</t>
   </si>
   <si>
     <t>alignment-renewal</t>
@@ -168,7 +168,7 @@
     <t>Alignment Renewal Due</t>
   </si>
   <si>
-    <t>The alignment period is ending and renewal action is required to continue services under the ACCESS Model.</t>
+    <t>The initial alignment period is ending and renewal action is required to continue services under the ACCESS Model.</t>
   </si>
   <si>
     <t>baseline-reporting-window</t>
@@ -177,7 +177,7 @@
     <t>Baseline Reporting Due</t>
   </si>
   <si>
-    <t>Baseline data must be reported within 60 days of alignment. The baseline data is due soon. Please submit the baseline data for the patient.</t>
+    <t>The baseline data report is due soon. If baseline reporting is not received within 60 days of alignment, the patient will be unaligned.</t>
   </si>
   <si>
     <t>quarterly-reporting-window</t>
@@ -186,7 +186,7 @@
     <t>Quarterly Reporting Due</t>
   </si>
   <si>
-    <t>The quarterly data report is due soon. Please submit the quarterly data for the patient.</t>
+    <t>The quarterly data report is due soon. Quarterly reporting must be submitted 70 to 110 days after the prior data submission.</t>
   </si>
   <si>
     <t>eoy-reporting-window</t>
@@ -195,7 +195,7 @@
     <t>End-of-Year Reporting Due</t>
   </si>
   <si>
-    <t>The end-of-year data report is due soon. Please submit the end-of-year data for the patient.</t>
+    <t>The end-of-year data report is due soon. End-of-year reporting must be submitted no later than 425 days from the date of alignment (365 days plus an additional 60 days).</t>
   </si>
   <si>
     <t>unalignment</t>
@@ -204,7 +204,7 @@
     <t>Unalignment Notice</t>
   </si>
   <si>
-    <t>The patient has been unaligned from the ACCESS Model. See the Beneficiary Alignment Report for additional information.</t>
+    <t>The patient has been unaligned from the ACCESS Model due to a change in eligibility status.</t>
   </si>
 </sst>
 </file>

--- a/CodeSystem-ACCESSEventTypeCS.xlsx
+++ b/CodeSystem-ACCESSEventTypeCS.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/CodeSystem/ACCESSEventTypeCS</t>
+    <t>https://dsacms.github.io/cmmi-access-model/CodeSystem/ACCESSEventTypeCS</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T16:03:26-05:00</t>
+    <t>2026-03-12T23:55:37-07:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSEventTypeCS.xlsx
+++ b/CodeSystem-ACCESSEventTypeCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T23:55:37-07:00</t>
+    <t>2026-04-24T13:45:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -150,7 +150,7 @@
     <t>Participant Lock-In Period Ending</t>
   </si>
   <si>
-    <t>The 3-month participant lock-in period is ending soon, allowing the patient to switch to a different participant if desired.</t>
+    <t>The 90-day participant lock-in period is ending soon, allowing the patient to switch to a different participant if desired.</t>
   </si>
   <si>
     <t>control-group-ending</t>

--- a/CodeSystem-ACCESSEventTypeCS.xlsx
+++ b/CodeSystem-ACCESSEventTypeCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSEventTypeCS.xlsx
+++ b/CodeSystem-ACCESSEventTypeCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSEventTypeCS.xlsx
+++ b/CodeSystem-ACCESSEventTypeCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSEventTypeCS.xlsx
+++ b/CodeSystem-ACCESSEventTypeCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSEventTypeCS.xlsx
+++ b/CodeSystem-ACCESSEventTypeCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
